--- a/corrected-bank-specimens-for-user/04-gcb/parsed-excel/GCB REPUBLIC HOUSE CASHBOOK CURRENT (100-026-024)-September,2023Q - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/04-gcb/parsed-excel/GCB REPUBLIC HOUSE CASHBOOK CURRENT (100-026-024)-September,2023Q - parsed.xlsx
@@ -436,7 +436,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-08T16:17:01.071Z</v>
+        <v>2026-07-14T13:50:03.786Z</v>
       </c>
     </row>
     <row r="5">

--- a/corrected-bank-specimens-for-user/04-gcb/parsed-excel/GCB REPUBLIC HOUSE CASHBOOK CURRENT (100-026-024)-September,2023Q - parsed.xlsx
+++ b/corrected-bank-specimens-for-user/04-gcb/parsed-excel/GCB REPUBLIC HOUSE CASHBOOK CURRENT (100-026-024)-September,2023Q - parsed.xlsx
@@ -436,7 +436,7 @@
         <v>Exported</v>
       </c>
       <c r="B4" t="str">
-        <v>2026-07-14T13:50:03.786Z</v>
+        <v>2026-07-17T19:29:57.648Z</v>
       </c>
     </row>
     <row r="5">
